--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=100_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=100_without_41.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4596231398115453</v>
+        <v>0.3870570406648615</v>
       </c>
       <c r="C3" t="n">
-        <v>1.698899393828432</v>
+        <v>1.706206585538167</v>
       </c>
       <c r="D3" t="n">
         <v>1.8</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7656527374030311</v>
+        <v>0.6347806048907366</v>
       </c>
       <c r="C4" t="n">
-        <v>2.038081860637842</v>
+        <v>2.24178376602259</v>
       </c>
       <c r="D4" t="n">
         <v>2.05</v>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.93928609533087</v>
+        <v>0.9392860953308709</v>
       </c>
       <c r="C6" t="n">
         <v>2.28094729631602</v>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.412799918321788</v>
+        <v>0.4127999183217883</v>
       </c>
       <c r="C7" t="n">
         <v>1.679362087964434</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8824062418672718</v>
+        <v>0.6671814063278472</v>
       </c>
       <c r="C10" t="n">
-        <v>1.573323574336965</v>
+        <v>1.585215479744732</v>
       </c>
       <c r="D10" t="n">
         <v>1.75</v>
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.849927452785844</v>
+        <v>0.8342409175141071</v>
       </c>
       <c r="C12" t="n">
-        <v>1.389833104176647</v>
+        <v>1.456151730781065</v>
       </c>
       <c r="D12" t="n">
         <v>1.4</v>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6574818705434353</v>
+        <v>0.7995621583000656</v>
       </c>
       <c r="C14" t="n">
-        <v>1.641209373827798</v>
+        <v>1.693372477186178</v>
       </c>
       <c r="D14" t="n">
         <v>1.55</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3833382435389791</v>
+        <v>0.2693026755562119</v>
       </c>
       <c r="C17" t="n">
-        <v>2.12926110986117</v>
+        <v>1.968184459954682</v>
       </c>
       <c r="D17" t="n">
         <v>2.8</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7593151492380799</v>
+        <v>0.7593151492380797</v>
       </c>
       <c r="C18" t="n">
         <v>2.783612351934546</v>
